--- a/maintenance/除外模本（XX公司XX等产品）.xlsx
+++ b/maintenance/除外模本（XX公司XX等产品）.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
   <si>
     <t>新增卫生材料告知单</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>27位医保编码</t>
+  </si>
+  <si>
+    <t>对应收费项目与材料编码请勿填写</t>
   </si>
   <si>
     <t>使用科室负责人：</t>
@@ -134,7 +137,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,6 +205,17 @@
     </font>
     <font>
       <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -715,137 +729,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -938,6 +952,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1214,6 +1234,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1542,11 +1569,11 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:12">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:15">
       <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="31" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -1573,11 +1600,14 @@
       <c r="J5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="31" t="s">
         <v>14</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>15</v>
+      </c>
+      <c r="O5" s="32" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" ht="18.75" spans="1:15">
@@ -1616,23 +1646,23 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A8" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="19"/>
       <c r="E8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
       <c r="K8" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
@@ -1658,12 +1688,12 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A10" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -1709,7 +1739,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1740,7 +1770,7 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -1844,23 +1874,23 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="28" customHeight="1" spans="1:15">
       <c r="A8" s="26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
       <c r="D8" s="27"/>
       <c r="E8" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
       <c r="H8" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="26"/>
       <c r="J8" s="26"/>
       <c r="K8" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" s="26"/>
       <c r="M8" s="26"/>
@@ -1869,20 +1899,20 @@
     </row>
     <row r="9" s="1" customFormat="1" ht="27" customHeight="1" spans="1:15">
       <c r="A9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="29"/>
       <c r="E9" s="30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="H9" s="28"/>
       <c r="I9" s="28"/>
       <c r="J9" s="28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K9" s="28"/>
       <c r="L9" s="28"/>
@@ -1927,7 +1957,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1958,7 +1988,7 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -2062,23 +2092,23 @@
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A8" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="19"/>
       <c r="E8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
       <c r="K8" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
@@ -2104,12 +2134,12 @@
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A10" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
       <c r="D10" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
